--- a/resumes/uae-job-tracker-categorized.xlsx
+++ b/resumes/uae-job-tracker-categorized.xlsx
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89945308caee8</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89945308caee8 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89cf5ce9cc34b</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e899494cedcd60</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e899494cedcd60 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89cfc2a56acd0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8994d82744ae3</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8994d82744ae3 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d0228492b70</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89951d50b68b7</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89951d50b68b7 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d089904515a</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89956b48c3cad</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89956b48c3cad | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d0ead50a17f</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8995bb9aefbbb</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8995bb9aefbbb | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d146678c6a2</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8995fe4f14b21</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8995fe4f14b21 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d1b128adb5c</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8996472185e94</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8996472185e94 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d20d8adcac1</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8996a624036db</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8996a624036db | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d28a4d760b1</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89945308caee8</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89945308caee8 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89cf5ce9cc34b</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e899494cedcd60</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e899494cedcd60 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89cfc2a56acd0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8994d82744ae3</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8994d82744ae3 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d0228492b70</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89951d50b68b7</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89951d50b68b7 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d089904515a</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89956b48c3cad</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89956b48c3cad | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d0ead50a17f</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8995bb9aefbbb</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8995bb9aefbbb | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d146678c6a2</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8995fe4f14b21</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8995fe4f14b21 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d1b128adb5c</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8996472185e94</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8996472185e94 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d20d8adcac1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8996a624036db</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8996a624036db | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d28a4d760b1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89945308caee8</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89945308caee8 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89cf5ce9cc34b</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e899494cedcd60</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e899494cedcd60 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89cfc2a56acd0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -11325,7 +11325,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8994d82744ae3</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8994d82744ae3 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d0228492b70</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89951d50b68b7</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89951d50b68b7 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d089904515a</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89956b48c3cad</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89956b48c3cad | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d0ead50a17f</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8995bb9aefbbb</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8995bb9aefbbb | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d146678c6a2</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8995fe4f14b21</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8995fe4f14b21 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d1b128adb5c</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8996472185e94</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8996472185e94 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d20d8adcac1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8996a624036db</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8996a624036db | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d28a4d760b1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89945308caee8</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89945308caee8 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89cf5ce9cc34b</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e899494cedcd60</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e899494cedcd60 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89cfc2a56acd0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8994d82744ae3</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8994d82744ae3 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d0228492b70</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89951d50b68b7</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89951d50b68b7 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d089904515a</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89956b48c3cad</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e89956b48c3cad | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d0ead50a17f</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8995bb9aefbbb</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8995bb9aefbbb | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d146678c6a2</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8995fe4f14b21</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8995fe4f14b21 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d1b128adb5c</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8996472185e94</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8996472185e94 | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d20d8adcac1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8996a624036db</t>
+          <t>Agency outreach sent with UAE Product Designer CV. Gmail sent id: 19e8996a624036db | Duplicate resend approved by user; updated/tighter agency CV sent. Gmail sent id: 19e89d28a4d760b1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
